--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1027,14 +1027,14 @@
           <t>将来推計</t>
         </is>
       </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>0.30</t>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>0.40</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎が未決定のため着手できない。構造と補正手順は整理済み。</t>
+          <t>見える化A系列の受領により基礎データの整理は完了した。人口の基礎が未決定のため推計に着手できない。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の決定。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の決定。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（5）将来推計に着手できない。人口の基礎が決まらないと認定率・見込量・保険料が順に決まらない。</t>
+          <t>仕様書４（5）将来推計の基礎は整理できたが、社人研推計を用いるか3町の推計へ差し替えるかの判断ができない。第2章第1節の町別の記述及び特定地域の判定（市町村単位）も確定しない。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1427,7 +1427,8 @@
         <is>
           <t>資料依頼No.3
 確認No.11
-別管理表B5</t>
+別管理表B5
+人口推計の基礎の検証07</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2136,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>①社人研推計（見える化の初期値）をそのまま用いる〈受託者の推奨〉／②3町の総合計画等による推計人口へ差し替える。②を選ぶ場合は差替えの根拠、社人研推計との差、差が生じる理由（社会増の見込み）を本文に明記する。</t>
+          <t>①社人研推計（見える化の初期値）をそのまま用いる〈受託者の推奨〉／②3町の総合計画等による推計人口へ差し替える／③社人研推計を基本とし東川町のみ感度分析として別途示す。②を選ぶ場合は差替えの根拠、社人研推計との差、差が生じる理由（社会増の見込み）を本文に明記する。判断材料は人口推計の基礎の検証07シートに示している。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4286,7 +4287,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎（方針の決定No.1）の決定後に着手する。自然体推計、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算。</t>
+          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。人口の基礎（方針の決定No.1）の決定後に推計に着手する。自然体推計、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4928,7 +4929,7 @@
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <is>
           <t>No.1 令和6〜8年度の事業実績
 No.2 3調査の第10期分
-No.9 町別住基人口</t>
+No.14 要介護度別認定者数</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>No.1 人口推計の基礎
+          <t>No.2 認定率のシナリオ
 No.13 自給率の掲載の可否</t>
         </is>
       </c>
@@ -1029,18 +1029,18 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>見える化A系列の受領により基礎データの整理は完了した。人口の基礎が未決定のため推計に着手できない。</t>
+          <t>人口の基礎が決定し、第1段階（人口と認定者数）を完了した。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>資料No.9、方針No.1〜No.5</t>
+          <t>資料No.14、方針No.2〜No.5</t>
         </is>
       </c>
     </row>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（13件）</t>
+          <t>資料の提供をお願いする事項（14件）</t>
         </is>
       </c>
     </row>
@@ -1434,518 +1434,542 @@
     </row>
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定するため、内訳がないと将来推計の第2段階に進めない。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。認定者数の合計は将来推計01〜04シートで推計済みである。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>将来推計07シートNo.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.9
 確認No.16</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.17
 別管理表B30</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>区域外の事業所が旭川市か他の市町村かを特定する。</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.18
 確認No.30</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.7</t>
-        </is>
-      </c>
-    </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.8
 確認No.23</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.5
 確認No.6・38</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>第1章第7節の訪問・通所困難地域が確定しない。第10期基本指針案の別表 一への対応が推量にとどまる。</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="4" t="n">
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。レッドチームレビューNo.15が未解消。</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr"/>
-      <c r="E19" s="3" t="inlineStr"/>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr"/>
+      <c r="E20" s="3" t="inlineStr"/>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-      <c r="G20" s="15" t="n"/>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="B21" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 要介護度別認定者数の実績（令和元年〜令和8年度・</t>
         </is>
       </c>
       <c r="D21" s="15" t="n"/>
@@ -1956,17 +1980,17 @@
       <c r="I21" s="8" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険</t>
+          <t>No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
         </is>
       </c>
       <c r="D22" s="15" t="n"/>
@@ -1977,17 +2001,17 @@
       <c r="I22" s="8" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>
@@ -1997,8 +2021,29 @@
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="8" t="n"/>
     </row>
-    <row r="25" ht="104" customHeight="1">
-      <c r="A25" s="11" t="inlineStr">
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="8" t="n"/>
+    </row>
+    <row r="26" ht="104" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2007,13 +2052,13 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C23:I23"/>
-    <mergeCell ref="A25:I25"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H17">
+  <conditionalFormatting sqref="H5:H18">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2031,7 +2076,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2131,17 +2176,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口推計の基礎</t>
+          <t>第10期の人口推計の基礎【決定済（R8.7.30）】</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>①社人研推計（見える化の初期値）をそのまま用いる〈受託者の推奨〉／②3町の総合計画等による推計人口へ差し替える／③社人研推計を基本とし東川町のみ感度分析として別途示す。②を選ぶ場合は差替えの根拠、社人研推計との差、差が生じる理由（社会増の見込み）を本文に明記する。判断材料は人口推計の基礎の検証07シートに示している。</t>
+          <t>①社人研推計（見える化の初期値）をそのまま用いる　←　採用。広域連合からの意向がない場合は見える化システムの値により進めるとの決定。②3町の総合計画等による推計人口への差替え、③東川町のみ感度分析として別途示す、は採らない。決定の記録は将来推計01シートに残している。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>第2章第1節及び第6章の全推計。以降の認定率・見込量・保険料がこれに依存する。</t>
+          <t>決定済。第2章第1節及び第6章の全推計の前提が確定した。将来推計の第1段階（人口と認定者数）に着手した。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2151,7 +2196,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>決定済</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -2162,7 +2207,8 @@
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>別管理表B5
-確認No.11</t>
+確認No.11
+将来推計01</t>
         </is>
       </c>
     </row>
@@ -2177,17 +2223,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>重度化の速度の置き方</t>
+          <t>階級別認定率のシナリオの選択</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>①全国並みに収束すると置く／②現状継続／③改善継続。認定率は年齢階級別に設定し、軽度と中重度で方向が異なることを反映する〈受託者の案〉。</t>
+          <t>①現状固定（令和8年の認定率で固定・自然体推計に相当）／②トレンド継続（令和元〜8年の変化を令和11年度まで延長）〈受託者の推奨〉／③令和元年水準へ回帰（上位ケース）。令和11年度の認定者数は①2,044人・②2,004人・③2,112人。②を基本とし③を保険料の安全側の確認として併用することを提案する。算定は将来推計03・04シートに示している。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>第6章第1節の認定者数見込み。</t>
+          <t>第6章第1節の認定者数見込み。第2段階（見込量）の前提。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2208,7 +2254,8 @@
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>別管理表B21
-確認No.29</t>
+確認No.29
+将来推計03・04</t>
         </is>
       </c>
     </row>
@@ -2927,7 +2974,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>No.1 第10期の人口推計の基礎、No.2 重度化の速度の置き方、No.3 施策効果の見込み方</t>
+          <t>No.1 第10期の人口推計の基礎【決定済（R8.7.、No.2 階級別認定率のシナリオの選択、No.3 施策効果の見込み方</t>
         </is>
       </c>
       <c r="D24" s="15" t="n"/>
@@ -4618,17 +4665,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>方針No.1 人口推計の基礎</t>
+          <t>資料No.14 要介護度別認定者数の実績</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>社人研推計を用いるか、3町の総合計画等による推計人口へ差し替えるか。</t>
+          <t>要支援1・2、要介護1〜5の別（令和元年〜令和8年度・各年3月末）。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（5）将来推計の着手。第2章第1節・第6章の全推計。</t>
+          <t>将来推計の第2段階（サービス見込量）の着手。方針No.1（人口推計の基礎）は令和8年7月30日に決定済み。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -4918,23 +4965,23 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（5）将来推計</t>
+          <t>仕様書４（5）将来推計 第2段階</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>資料No.9（町別住基人口）→方針No.1（人口推計の基礎）</t>
+          <t>資料No.14（要介護度別認定者数）→方針No.2（認定率のシナリオ）</t>
         </is>
       </c>
       <c r="D23" s="8" t="n"/>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>第6章の全体（認定者数・見込量・給付費・保険料）が未算定。計画素案の第6章が［要協議］［要確認］のまま。令和8年12月の工程（素案確定版）に間に合わせるには令和8年9月中に方針No.1の決定が必要。</t>
+          <t>第1段階（人口と認定者数）は完了した。サービス見込量は要介護度別の利用率により算定するため、内訳がないと第2段階に進めない。令和8年12月の工程（素案確定版）に間に合わせるには令和8年9月中の受領と令和8年10月中の方針No.2の決定が必要。</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5066,7 @@
     <row r="28" ht="104" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>注1）段1（令和8年8月）の5件は、いずれも他の事項の解消を待たずに決めていただけるものである。このうち資料No.1・No.2は仕様書の業務が完了しない資料であり、日程No.1は工程の起点、方針No.13と成果品No.3は図表を作る前提である。注2）段2以降は上流の解消が前提となる。特に方針No.1（人口推計の基礎）は、第6章の全体がこれに依存するため最も影響が大きい。令和8年12月の工程（計画素案の確定版）に間に合わせるには、令和8年9月中の決定が必要である。注3）告示待ち（段5）は令和8年末から令和9年初となる見込みである。保険料の最終確定はそれ以降であり、計画最終案（令和9年2月）の直前となる。この期間の作業量を見込んで工程を組む必要がある。</t>
+          <t>注0）方針No.1（人口推計の基礎）は令和8年7月30日に決定し、社人研推計をそのまま用いることとなった。将来推計の第1段階（人口と認定者数）は完了している。注1）段1（令和8年8月）の5件は、いずれも他の事項の解消を待たずに決めていただけるものである。このうち資料No.1・No.2は仕様書の業務が完了しない資料であり、日程No.1は工程の起点、方針No.13と成果品No.3は図表を作る前提である。注2）段2以降は上流の解消が前提となる。特に方針No.1（人口推計の基礎）は、第6章の全体がこれに依存するため最も影響が大きい。令和8年12月の工程（計画素案の確定版）に間に合わせるには、令和8年9月中の決定が必要である。注3）告示待ち（段5）は令和8年末から令和9年初となる見込みである。保険料の最終確定はそれ以降であり、計画最終案（令和9年2月）の直前となる。この期間の作業量を見込んで工程を組む必要がある。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎が決定し、第1段階（人口と認定者数）を完了した。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の第10期分（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎の決定（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の第10期分（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の決定。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の選択（方針No.1）の判断材料。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2176,17 +2176,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>第10期の人口推計の基礎【決定済（R8.7.30）】</t>
+          <t>第10期の人口推計の基礎【受託者の案・意向確認待ち】</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>①社人研推計（見える化の初期値）をそのまま用いる　←　採用。広域連合からの意向がない場合は見える化システムの値により進めるとの決定。②3町の総合計画等による推計人口への差替え、③東川町のみ感度分析として別途示す、は採らない。決定の記録は将来推計01シートに残している。</t>
+          <t>①社人研推計（見える化の初期値）をそのまま用いる　←　受託者の案。②3町の総合計画等による推計人口への差替え、③東川町のみ感度分析として別途示す。受託者は①を案とし、これを作業上の前提として仮に置いたうえで第1段階を試算している。試算の前提は将来推計01シートに記録している。キックオフ会議でご意向を確認する（ヒアリングシート項目6-1）。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>決定済。第2章第1節及び第6章の全推計の前提が確定した。将来推計の第1段階（人口と認定者数）に着手した。</t>
+          <t>第2章第1節及び第6章の全推計の前提。②又は③のご意向がある場合は第1段階を再計算する。</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>決定済</t>
+          <t>確認待ち</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>No.1 第10期の人口推計の基礎【決定済（R8.7.、No.2 階級別認定率のシナリオの選択、No.3 施策効果の見込み方</t>
+          <t>No.1 第10期の人口推計の基礎【受託者の案・意向確、No.2 階級別認定率のシナリオの選択、No.3 施策効果の見込み方</t>
         </is>
       </c>
       <c r="D24" s="15" t="n"/>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>自給率・地域差指数・保険料の管内比較を第2章第2節・第3節、第3章第5節、第6章第5節・第6節へ反映する。δの掲載の可否（方針の決定No.13）の決定後に確定する。</t>
+          <t>自給率・地域差指数・保険料の管内比較を第2章第2節・第3節、第3章第5節、第6章第5節・第6節へ反映する。δの掲載の可否（方針の決定No.13）のご意向の確認後に確定する。</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。人口の基礎（方針の決定No.1）の決定後に推計に着手する。自然体推計、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算。</t>
+          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。第1段階（人口と認定者数）は、人口の基礎（方針の決定No.1）について受託者の案を仮に置いて試算済み。ご意向の確認後に前提を確定する。自然体推計、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -4376,7 +4376,7 @@
     <row r="13" ht="104" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>注1）No.6（将来推計）とNo.7（委員会資料原案）は、それぞれ方針の決定No.1と日程・体制No.1の確定を待っている。この2件が全体の工程で最も大きな待ちである。注2）No.1の見える化からの追加取得は受託者側で試行するが、システムに当広域連合のデータ登録がない系列（δの過年度値、H1・H2、J、L）は取得できない可能性がある。取得できない場合は代替手段を資料6に記載する。注3）No.2〜No.5は資料の受領を待たずに進められる作業である。令和8年8月中に完了させ、計画素案の次稿（第11稿）に反映する。</t>
+          <t>注1）No.6（将来推計）とNo.7（委員会資料原案）は、それぞれ方針の決定No.1のご意向の確認と日程・体制No.1の確定を待っている。この2件が全体の工程で最も大きな待ちである。注2）No.1の見える化からの追加取得は受託者側で試行するが、システムに当広域連合のデータ登録がない系列（δの過年度値、H1・H2、J、L）は取得できない可能性がある。取得できない場合は代替手段を資料6に記載する。注3）No.2〜No.5は資料の受領を待たずに進められる作業である。令和8年8月中に完了させ、計画素案の次稿（第11稿）に反映する。</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）の着手。方針No.1（人口推計の基礎）は令和8年7月30日に決定済み。</t>
+          <t>将来推計の第2段階（サービス見込量）の着手。方針No.1（人口推計の基礎）は受託者の案を仮に置いて試算済み。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -5066,7 +5066,7 @@
     <row r="28" ht="104" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t>注0）方針No.1（人口推計の基礎）は令和8年7月30日に決定し、社人研推計をそのまま用いることとなった。将来推計の第1段階（人口と認定者数）は完了している。注1）段1（令和8年8月）の5件は、いずれも他の事項の解消を待たずに決めていただけるものである。このうち資料No.1・No.2は仕様書の業務が完了しない資料であり、日程No.1は工程の起点、方針No.13と成果品No.3は図表を作る前提である。注2）段2以降は上流の解消が前提となる。特に方針No.1（人口推計の基礎）は、第6章の全体がこれに依存するため最も影響が大きい。令和8年12月の工程（計画素案の確定版）に間に合わせるには、令和8年9月中の決定が必要である。注3）告示待ち（段5）は令和8年末から令和9年初となる見込みである。保険料の最終確定はそれ以降であり、計画最終案（令和9年2月）の直前となる。この期間の作業量を見込んで工程を組む必要がある。</t>
+          <t>注0）方針No.1（人口推計の基礎）は、社人研推計をそのまま用いることを受託者の案とし、これを仮に置いて将来推計の第1段階（人口と認定者数）を試算した段階である。基礎の採用はキックオフ会議でご意向を確認する。注1）段1（令和8年8月）の5件は、いずれも他の事項の解消を待たずに決めていただけるものである。このうち資料No.1・No.2は仕様書の業務が完了しない資料であり、日程No.1は工程の起点、方針No.13と成果品No.3は図表を作る前提である。注2）段2以降は上流の解消が前提となる。特に方針No.1（人口推計の基礎）は、第6章の全体がこれに依存するため最も影響が大きい。令和8年12月の工程（計画素案の確定版）に間に合わせるには、令和8年9月中の決定が必要である。注3）告示待ち（段5）は令和8年末から令和9年初となる見込みである。保険料の最終確定はそれ以降であり、計画最終案（令和9年2月）の直前となる。この期間の作業量を見込んで工程を組む必要がある。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -973,18 +973,18 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査は完了。他3調査の第10期分が未受領。</t>
+          <t>4調査すべてを受領し集計した。3調査は点検事項29件（重大3件）の解消を待って計画本文へ反映する。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>資料No.2</t>
+          <t>3調査の点検02</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の第10期分（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大3件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1340,31 +1340,31 @@
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）</t>
+          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
+          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の選択（方針No.1）の判断材料。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（3）が完了しない。第2章第5節・第6節、第5章基本目標2・4の根拠が令和5年調査のままとなる。第4章のKPI4項目の基準値が確定しない。</t>
+          <t>仕様書４（5）将来推計の基礎は整理できたが、社人研推計を用いるか3町の推計へ差し替えるかの判断ができない。第2章第1節の町別の記述及び特定地域の判定（市町村単位）も確定しない。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1378,52 +1378,6 @@
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.14
-確認No.8・9</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の選択（方針No.1）の判断材料。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>仕様書４（5）将来推計の基礎は整理できたが、社人研推計を用いるか3町の推計へ差し替えるかの判断ができない。第2章第1節の町別の記述及び特定地域の判定（市町村単位）も確定しない。</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.3
 確認No.11
@@ -1432,9 +1386,54 @@
         </is>
       </c>
     </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定するため、内訳がないと将来推計の第2段階に進めない。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。認定者数の合計は将来推計01〜04シートで推計済みである。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>将来推計07シートNo.2</t>
+        </is>
+      </c>
+    </row>
     <row r="8" ht="76" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -1443,27 +1442,27 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項29件の解消待ち】</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定するため、内訳がないと将来推計の第2段階に進めない。</t>
+          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。認定者数の合計は将来推計01〜04シートで推計済みである。</t>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>最高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -1473,7 +1472,9 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>将来推計07シートNo.2</t>
+          <t>資料依頼No.14
+確認No.8・9
+3調査の点検02</t>
         </is>
       </c>
     </row>
@@ -1965,11 +1966,11 @@
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 要介護度別認定者数の実績（令和元年〜令和8年度・</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 要介護度別認定者数の実績（令和元年〜令和8年度・</t>
         </is>
       </c>
       <c r="D21" s="15" t="n"/>
@@ -1986,11 +1987,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
         </is>
       </c>
       <c r="D22" s="15" t="n"/>
@@ -4515,17 +4516,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>資料No.2 3調査の第10期分</t>
+          <t>資料No.2 3調査の第10期分の点検事項の解消</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善・居所変更実態・介護人材実態の各調査。</t>
+          <t>重大3件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否）の方針と、事業所への照会の要否・方法。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（3）の完了。代表KPI H06・H11・H13・H14の基準値。</t>
+          <t>仕様書４（3）の完了。代表KPI H06・H11・H13・H14の基準値。第6章第2節（見込量）・第4節（施設整備）の根拠。</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -5048,18 +5049,18 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>資料No.2（3調査の第10期分）</t>
+          <t>点検事項の重大3件の取扱い（No.1〜No.3）</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>4調査横断のクロス集計ができない。代表KPI H06・H11・H13・H14の基準値が令和5年調査のままとなる。</t>
+          <t>介護職員の総数、小規模多機能の見込量、地区別分析の可否が決まらない。代表KPI H06・H11・H13・H14の基準値が確定しない。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計した。3調査は点検事項29件（重大3件）の解消を待って計画本文へ反映する。</t>
+          <t>4調査すべてを受領し集計した。3調査は点検事項31件（重大4件）の解消を待って計画本文へ反映する。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大3件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大4件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項29件の解消待ち】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項31件の解消待ち】</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>重大3件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否）の方針と、事業所への照会の要否・方法。</t>
+          <t>重大4件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否、老健・通所リハの介護職員数の範囲）の方針と、事業所への照会の要否・方法。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>点検事項の重大3件の取扱い（No.1〜No.3）</t>
+          <t>点検事項の重大4件の取扱い（No.1〜No.3・No.31）</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -642,7 +642,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>必要事項の一覧（令和8年7月30日現在）</t>
+          <t>必要事項の一覧（令和8年8月4日現在）</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>類似保険者の選定条件が未決定。自給率・地域差指数・保険料は受領し分析済み。</t>
+          <t>類似保険者の選定条件が未決定。自給率・地域差指数・保険料は受領し分析済み。サービス提供体制は3調査と見える化K・M2系列の突合により把握範囲を確定した。</t>
         </is>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。第2段階（見込量）は要介護度別認定者数の受領を待つ。</t>
+          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。要介護度別認定者数は見える化B3系列で受領済み。第2段階（見込量）はサービス種別・要介護度別の受給者数を待つ。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（14件）</t>
+          <t>資料の提供をお願いする事項（15件）</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>要介護度別認定者数の実績（令和元年〜令和8年度・各年3月末）</t>
+          <t>サービス種別・要介護度別の受給者数（令和4〜7年度）【要介護度別認定者数は見える化B3系列により令和8年3月末まで受領済】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別。サービス見込量は要介護度別の利用率により算定するため、内訳がないと将来推計の第2段階に進めない。</t>
+          <t>サービス見込量は要介護度別の利用率（受給者数÷認定者数）により算定する。要介護度別の認定者数は令和8年8月4日に見える化B3系列で受領した（要介護認定データの確認 01シート）。残るのは分子となるサービス種別・要介護度別の受給者数である。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。認定者数の合計は将来推計01〜04シートで推計済みである。</t>
+          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。見える化D系列で代替できるかを受託者側で確認中である。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1427,7 +1427,8 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>将来推計07シートNo.2</t>
+          <t>将来推計07シートNo.2
+認定データの確認06</t>
         </is>
       </c>
     </row>
@@ -1893,105 +1894,129 @@
     </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>認定データの確認06シートNo.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G19" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr"/>
-      <c r="E20" s="3" t="inlineStr"/>
-      <c r="F20" s="3" t="inlineStr"/>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="14" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
+      <c r="F21" s="3" t="inlineStr"/>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n">
+      <c r="B22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 要介護度別認定者数の実績（令和元年〜令和8年度・</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-      <c r="G21" s="15" t="n"/>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n">
-        <v>8</v>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 サービス種別・要介護度別の受給者数（令和4〜7年</t>
         </is>
       </c>
       <c r="D22" s="15" t="n"/>
@@ -2002,17 +2027,17 @@
       <c r="I22" s="8" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>
@@ -2023,17 +2048,17 @@
       <c r="I23" s="8" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
         </is>
       </c>
       <c r="D24" s="15" t="n"/>
@@ -2043,8 +2068,29 @@
       <c r="H24" s="15" t="n"/>
       <c r="I24" s="8" t="n"/>
     </row>
-    <row r="26" ht="104" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="8" t="n"/>
+    </row>
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2055,11 +2101,11 @@
     <mergeCell ref="C23:I23"/>
     <mergeCell ref="C22:I22"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="C24:I24"/>
-    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="C25:I25"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H18">
+  <conditionalFormatting sqref="H5:H19">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2077,7 +2123,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4666,17 +4712,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>資料No.14 要介護度別認定者数の実績</t>
+          <t>資料No.14 サービス種別・要介護度別の受給者数</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>要支援1・2、要介護1〜5の別（令和元年〜令和8年度・各年3月末）。</t>
+          <t>要介護度別認定者数は見える化B3系列により令和8年3月末まで受領済み（要介護認定データの確認 01シート）。残るのはサービス種別ごとの利用率の算定に要する受給者数である。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）の着手。方針No.1（人口推計の基礎）は受託者の案を仮に置いて試算済み。</t>
+          <t>将来推計の第2段階（サービス見込量）の着手。</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。要介護度別認定者数は見える化B3系列で受領済み。第2段階（見込量）はサービス種別・要介護度別の受給者数を待つ。</t>
+          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）は見える化B3・D45・D46系列により閉じ、令和7年度の実績を1％未満の差で再現することを確認した。残るのは利用率と1人当たり利用日数の置き方のご意向の確認である。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -1388,7 +1388,7 @@
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
@@ -1397,81 +1397,35 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>サービス種別・要介護度別の受給者数（令和4〜7年度）【要介護度別認定者数は見える化B3系列により令和8年3月末まで受領済】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項31件の解消待ち】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>サービス見込量は要介護度別の利用率（受給者数÷認定者数）により算定する。要介護度別の認定者数は令和8年8月4日に見える化B3系列で受領した（要介護認定データの確認 01シート）。残るのは分子となるサービス種別・要介護度別の受給者数である。</t>
+          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>将来推計の第2段階（サービス見込量）に進めない。第6章第2節・第3節が算定できない。見える化D系列で代替できるかを受託者側で確認中である。</t>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>最高</t>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>確認待ち</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>将来推計07シートNo.2
-認定データの確認06</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項31件の解消待ち】</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.14
 確認No.8・9
@@ -1479,28 +1433,74 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.9
+確認No.16</t>
+        </is>
+      </c>
+    </row>
     <row r="9" ht="76" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・国保連</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
+          <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1520,14 +1520,14 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.9
-確認No.16</t>
+          <t>資料依頼No.17
+別管理表B30</t>
         </is>
       </c>
     </row>
     <row r="10" ht="76" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -1536,17 +1536,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+          <t>指定事業所台帳（区域外事業所の所在地）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
+          <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1566,33 +1566,33 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.17
-別管理表B30</t>
+          <t>資料依頼No.18
+確認No.30</t>
         </is>
       </c>
     </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>発注者・国保連</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。</t>
+          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1612,33 +1612,32 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.18
-確認No.30</t>
+          <t>資料依頼No.7</t>
         </is>
       </c>
     </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
+          <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
+          <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。</t>
+          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1658,13 +1657,14 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.7</t>
+          <t>資料依頼No.8
+確認No.23</t>
         </is>
       </c>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1673,22 +1673,22 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
+          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
@@ -1703,38 +1703,38 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.8
-確認No.23</t>
+          <t>資料依頼No.5
+確認No.6・38</t>
         </is>
       </c>
     </row>
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>北海道・広域連合</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+          <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
+          <t>第1章第7節の訪問・通所困難地域が確定しない。第10期基本指針案の別表 一への対応が推量にとどまる。</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G14" s="9" t="inlineStr">
@@ -1749,33 +1749,33 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.5
-確認No.6・38</t>
+          <t>資料依頼No.2
+確認No.15</t>
         </is>
       </c>
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>北海道・広域連合</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
+          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>第1章第7節の訪問・通所困難地域が確定しない。第10期基本指針案の別表 一への対応が推量にとどまる。</t>
+          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1795,8 +1795,7 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.2
-確認No.15</t>
+          <t>受給者数データの確認06シートNo.1・No.9</t>
         </is>
       </c>
     </row>
@@ -2012,11 +2011,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4、No.14 サービス種別・要介護度別の受給者数（令和4〜7年</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4</t>
         </is>
       </c>
       <c r="D22" s="15" t="n"/>
@@ -2033,11 +2032,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -729,7 +729,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -1029,18 +1029,18 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）は見える化B3・D45・D46系列により閉じ、令和7年度の実績を1％未満の差で再現することを確認した。残るのは利用率と1人当たり利用日数の置き方のご意向の確認である。</t>
+          <t>人口の基礎は受託者の案を仮に置いて第1段階（人口と認定者数）を試算した。基礎の採用はご意向の確認待ち。第2段階の算定チェーン（認定者数×利用率×1人当たり利用日数）は見える化B3・D45・D46系列により閉じ、令和7年度の実績を1％未満の差で再現することを確認した。第2段階（サービス見込量）は令和7年度の利用率・1人当たり利用日数で固定する案を基本に試算し、趨勢を見込む場合を感度分析として併記した。残るのは置き方のご意向の確認と第3段階（給付費・保険料）である。</t>
         </is>
       </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>資料No.14、方針No.2〜No.5</t>
+          <t>資料No.14、方針No.2〜No.5・No.18・No.19</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大4件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年7月30日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大4件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月4日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2153,7 +2153,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>決定をお願いする事項（17件）</t>
+          <t>決定をお願いする事項（19件）</t>
         </is>
       </c>
     </row>
@@ -2986,83 +2986,131 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22" ht="88" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>推計の前提</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>要介護度別の利用率の置き方【受託者の案・意向確認待ち】</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>①令和7年度の利用率で固定する　←　受託者の案。②令和5〜7年度の趨勢を令和11年度まで延長する、③施策効果を見込んで在宅の利用率を引き上げる。受託者は①を案とし、②を感度分析として併記した（将来推計 第2段階 05シート）。②の場合、在宅は＋6.7％、施設は▲9.3％となる。ヒアリングシート項目6-3でご意向を確認する。</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節のサービス見込量。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階 00・05シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="88" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>推計の前提</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>受給者1人当たりの利用日数・回数の置き方【受託者の案・意向確認待ち】</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>①令和7年度の値で固定する　←　受託者の案。②令和5〜7年度の趨勢を延長する。受託者は①を案とし、②を感度分析として併記した（将来推計 第2段階 05シート）。②の場合、訪問介護が＋23.7％（月15,645回→19,351回）と最も大きく動く。訪問介護の1人当たり利用回数は平成26年度22回から令和7年度55回へ2.5倍となっており、この趨勢を第10期に延長してよいかの判断を要する。ヒアリングシート項目6-4でご意向を確認する。</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節のサービス見込量、第3節の給付費。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>将来推計 第2段階 00・05シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>推計の前提</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>No.1 第10期の人口推計の基礎【受託者の案・意向確、No.2 階級別認定率のシナリオの選択、No.3 施策効果の見込み方</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>財政</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>No.4 基金の取崩方針と第10期の保険料水準、No.5 第10期の所得段階の設計</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="8" t="n"/>
+      <c r="D25" s="3" t="inlineStr"/>
+      <c r="E25" s="3" t="inlineStr"/>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr"/>
     </row>
     <row r="26" ht="26" customHeight="1">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>整備方針</t>
+          <t>推計の前提</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>No.6 24時間対応サービスの確保方策、No.7 施設・居住系の整備方針</t>
+          <t>No.1 第10期の人口推計の基礎【受託者の案・意向確、No.2 階級別認定率のシナリオの選択、No.3 施策効果の見込み方、No.18 要介護度別の利用率の置き方【受託者の案・意向、No.19 受給者1人当たりの利用日数・回数の置き方【受</t>
         </is>
       </c>
       <c r="D26" s="15" t="n"/>
@@ -3075,15 +3123,15 @@
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>圏域</t>
+          <t>財政</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.8 日常生活圏域の設定</t>
+          <t>No.4 基金の取崩方針と第10期の保険料水準、No.5 第10期の所得段階の設計</t>
         </is>
       </c>
       <c r="D27" s="15" t="n"/>
@@ -3096,7 +3144,7 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="17" t="inlineStr">
         <is>
-          <t>評価の記述</t>
+          <t>整備方針</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
@@ -3104,7 +3152,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.9 第9期の給付水準の評価の枠組み、No.10 第9期の代表KPIの評価の表現</t>
+          <t>No.6 24時間対応サービスの確保方策、No.7 施設・居住系の整備方針</t>
         </is>
       </c>
       <c r="D28" s="15" t="n"/>
@@ -3117,15 +3165,15 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
-          <t>指標の定義</t>
+          <t>圏域</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.11 代表KPI16項目のデータ源と定義、No.12 地域差指数の分解を要因の按分に用いない方針</t>
+          <t>No.8 日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D29" s="15" t="n"/>
@@ -3138,7 +3186,7 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="17" t="inlineStr">
         <is>
-          <t>掲載の可否</t>
+          <t>評価の記述</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
@@ -3146,7 +3194,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.13 介護サービス自給率（δ）の計画本文への掲載、No.14 給付費の地域内還流を整備の意義とするか</t>
+          <t>No.9 第9期の給付水準の評価の枠組み、No.10 第9期の代表KPIの評価の表現</t>
         </is>
       </c>
       <c r="D30" s="15" t="n"/>
@@ -3159,7 +3207,7 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
         <is>
-          <t>3町との関係</t>
+          <t>指標の定義</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
@@ -3167,7 +3215,7 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>No.15 3町計画への共通KPIの掲載、No.16 用語の統一</t>
+          <t>No.11 代表KPI16項目のデータ源と定義、No.12 地域差指数の分解を要因の按分に用いない方針</t>
         </is>
       </c>
       <c r="D31" s="15" t="n"/>
@@ -3180,15 +3228,15 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>評価の仕組み</t>
+          <t>掲載の可否</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>No.17 自己評価の様式と評価の段階</t>
+          <t>No.13 介護サービス自給率（δ）の計画本文への掲載、No.14 給付費の地域内還流を整備の意義とするか</t>
         </is>
       </c>
       <c r="D32" s="15" t="n"/>
@@ -3198,18 +3246,18 @@
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="8" t="n"/>
     </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>策定委員会の付議事項</t>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>3町との関係</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>No.7 施設・居住系の整備方針、No.8 日常生活圏域の設定、No.9 第9期の給付水準の評価の枠組み、No.10 第9期の代表KPIの評価の表現、No.14 給付費の地域内還流を整備の意義とするか</t>
+          <t>No.15 3町計画への共通KPIの掲載、No.16 用語の統一</t>
         </is>
       </c>
       <c r="D33" s="15" t="n"/>
@@ -3219,8 +3267,50 @@
       <c r="H33" s="15" t="n"/>
       <c r="I33" s="8" t="n"/>
     </row>
-    <row r="35" ht="104" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>評価の仕組み</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>No.17 自己評価の様式と評価の段階</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="8" t="n"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>策定委員会の付議事項</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>No.7 施設・居住系の整備方針、No.8 日常生活圏域の設定、No.9 第9期の給付水準の評価の枠組み、No.10 第9期の代表KPIの評価の表現、No.14 給付費の地域内還流を整備の意義とするか</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="8" t="n"/>
+    </row>
+    <row r="37" ht="104" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>注1）推計の前提（No.1〜No.3）と財政（No.4・No.5）は、この順に決めていただく必要がある。人口の基礎（No.1）→重度化の速度（No.2）→施策効果（No.3）→見込量→基金・保険料（No.4・No.5）と依存する（07シート）。注2）掲載の可否（No.13・No.14）は、図表を作る前に確認を要するものである。δは「本指標は自治体向けのため取り扱いに注意」と明記されている。注3）〈受託者の案〉は、根拠を示した上での提案である。採否の判断をいただければ、その内容で確定する。受託者の案に根拠がない事項（No.4の基金の取崩額など）は選択肢のみを示している。</t>
         </is>
@@ -3232,16 +3322,16 @@
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C26:I26"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C34:I34"/>
     <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C24:I24"/>
     <mergeCell ref="C30:I30"/>
     <mergeCell ref="C32:I32"/>
     <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C25:I25"/>
     <mergeCell ref="C27:I27"/>
-    <mergeCell ref="A35:I35"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H21">
+  <conditionalFormatting sqref="H5:H23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -3259,7 +3349,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4380,7 +4470,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。第1段階（人口と認定者数）は、人口の基礎（方針の決定No.1）について受託者の案を仮に置いて試算済み。ご意向の確認後に前提を確定する。自然体推計、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算。</t>
+          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。第1段階（人口と認定者数）は、人口の基礎（方針の決定No.1）について受託者の案を仮に置いて試算済み。ご意向の確認後に前提を確定する。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案（方針の決定No.18・No.19）を基本とし、趨勢を見込む場合を感度分析として併記して試算済み。残るのは第3段階（給付費・保険料）と、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算である。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4296,7 +4296,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>受託者が自ら行う作業（7件）</t>
+          <t>受託者が自ら行う作業（8件）</t>
         </is>
       </c>
     </row>
@@ -4361,41 +4361,41 @@
     </row>
     <row r="6" ht="64" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>レッドチームレビュー29件の残る対応</t>
+          <t>介護サービス情報公表システムからの事業所別従業者数の取得と突合</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>記述の修正により対応できる22件のうち、No.19〜26・No.29の9件は改める記述を確定して各成果物へ反映する。資料の受領を要する7件は資料の到着後に対応する。</t>
+          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項31件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>確認待ち</t>
         </is>
       </c>
     </row>
     <row r="7" ht="64" customHeight="1">
       <c r="A7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>主張の根拠水準の記述ルールの全成果物への適用</t>
+          <t>レッドチームレビュー29件の残る対応</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>54主張のうちE4（推論）10件・E5（仮説）3件について、水準に応じた語尾と併記事項を統一する。禁止する記述5件（「〜に由来する」等）を全成果物から除く。</t>
+          <t>記述の修正により対応できる22件のうち、No.19〜26・No.29の9件は改める記述を確定して各成果物へ反映する。資料の受領を要する7件は資料の到着後に対応する。</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -4411,21 +4411,21 @@
     </row>
     <row r="8" ht="64" customHeight="1">
       <c r="A8" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析結果の計画本文への反映</t>
+          <t>主張の根拠水準の記述ルールの全成果物への適用</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>調査クロス集計・分析24シートの結果を第2章第4節・第5章基本目標1へ反映する。小学校区12地区別の分析、年齢調整による地域比較を含む。</t>
+          <t>54主張のうちE4（推論）10件・E5（仮説）3件について、水準に応じた語尾と併記事項を統一する。禁止する記述5件（「〜に由来する」等）を全成果物から除く。</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.8</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4436,16 +4436,16 @@
     </row>
     <row r="9" ht="64" customHeight="1">
       <c r="A9" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>地域差の分析の計画本文への反映</t>
+          <t>健康とくらしの調査の分析結果の計画本文への反映</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>自給率・地域差指数・保険料の管内比較を第2章第2節・第3節、第3章第5節、第6章第5節・第6節へ反映する。δの掲載の可否（方針の決定No.13）のご意向の確認後に確定する。</t>
+          <t>調査クロス集計・分析24シートの結果を第2章第4節・第5章基本目標1へ反映する。小学校区12地区別の分析、年齢調整による地域比較を含む。</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -4461,56 +4461,81 @@
     </row>
     <row r="10" ht="64" customHeight="1">
       <c r="A10" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>将来推計の実施</t>
+          <t>地域差の分析の計画本文への反映</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。第1段階（人口と認定者数）は、人口の基礎（方針の決定No.1）について受託者の案を仮に置いて試算済み。ご意向の確認後に前提を確定する。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案（方針の決定No.18・No.19）を基本とし、趨勢を見込む場合を感度分析として併記して試算済み。残るのは第3段階（給付費・保険料）と、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算である。</t>
+          <t>自給率・地域差指数・保険料の管内比較を第2章第2節・第3節、第3章第5節、第6章第5節・第6節へ反映する。δの掲載の可否（方針の決定No.13）のご意向の確認後に確定する。</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>R8.10〜12</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>未着手</t>
+          <t>実施中</t>
         </is>
       </c>
     </row>
     <row r="11" ht="64" customHeight="1">
       <c r="A11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>将来推計の実施</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>見える化A系列（人口・2000〜2050年）の受領により基礎データの整理は完了した（人口推計の基礎の検証9シート）。第1段階（人口と認定者数）は、人口の基礎（方針の決定No.1）について受託者の案を仮に置いて試算済み。ご意向の確認後に前提を確定する。第2段階（サービス見込量）は、利用率と1人当たり利用日数・回数を令和7年度の値で固定する案（方針の決定No.18・No.19）を基本とし、趨勢を見込む場合を感度分析として併記して試算済み。残るのは第3段階（給付費・保険料）と、施策反映後の見込量、複数シナリオ（基本／需要上振れ／供給制約／基金活用）の試算である。</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>R8.10〜12</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="64" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>第1回委員会資料原案の作成</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>開催日程（日程・体制No.1）の確定後に着手する。方針の決定のうち策定委員会に付議する事項を整理する。</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="104" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+    <row r="14" ht="104" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>注1）No.6（将来推計）とNo.7（委員会資料原案）は、それぞれ方針の決定No.1のご意向の確認と日程・体制No.1の確定を待っている。この2件が全体の工程で最も大きな待ちである。注2）No.1の見える化からの追加取得は受託者側で試行するが、システムに当広域連合のデータ登録がない系列（δの過年度値、H1・H2、J、L）は取得できない可能性がある。取得できない場合は代替手段を資料6に記載する。注3）No.2〜No.5は資料の受領を待たずに進められる作業である。令和8年8月中に完了させ、計画素案の次稿（第11稿）に反映する。</t>
         </is>
@@ -4519,9 +4544,9 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E11">
+  <conditionalFormatting sqref="E5:E12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -4539,7 +4564,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E5:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E5:E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計した。3調査は点検事項31件（重大4件）の解消を待って計画本文へ反映する。</t>
+          <t>4調査すべてを受領し集計した。3調査は点検事項32件（重大5件）の解消を待って計画本文へ反映する。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大4件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月4日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大5件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月4日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項31件の解消待ち】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項32件の解消待ち】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が3件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。</t>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。残るのは入所者数・空床・休止床と、特養・老健・グループホームの定員である（住まいと施設の公表名簿との突合 06シート）。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項31件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
+          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項32件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>重大4件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否、老健・通所リハの介護職員数の範囲）の方針と、事業所への照会の要否・方法。</t>
+          <t>重大5件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否、老健・通所リハの介護職員数の範囲）の方針と、事業所への照会の要否・方法。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>点検事項の重大4件の取扱い（No.1〜No.3・No.31）</t>
+          <t>点検事項の重大5件の取扱い（No.1〜No.3・No.31）</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1710,229 +1710,229 @@
     </row>
     <row r="14" ht="76" customHeight="1">
       <c r="A14" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>受給者数データの確認06シートNo.1・No.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>美瑛町・3町</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>小学校区と日常生活圏域の対応関係</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.12
+確認No.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>受託者の評価との対照。評価の枠組みの整理。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>第3章の評価が受託者の評価のみとなる。レッドチームレビューNo.15が未解消。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.15
+確認No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>認定データの確認06シートNo.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>第1章第7節の訪問・通所困難地域が確定しない。第10期基本指針案の別表 一への対応が推量にとどまる。</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>受領済</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>受給者数データの確認06シートNo.1・No.9</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="4" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>美瑛町・3町</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.12
-確認No.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>受託者の評価との対照。評価の枠組みの整理。</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>第3章の評価が受託者の評価のみとなる。レッドチームレビューNo.15が未解消。</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.15
-確認No.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>認定データの確認06シートNo.5</t>
         </is>
       </c>
     </row>
@@ -2032,11 +2032,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.10 訪問系・通所系事業所の運営規程における「通常の事、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
       <c r="D25" s="15" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1536,12 +1536,12 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>指定事業所台帳（区域外事業所の所在地）</t>
+          <t>指定事業所台帳（区域外事業所の所在地、及び地域密着型サービスの定員・休止の状況）</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。</t>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。あわせて、グループホームくるみの郷（東川町・有限会社プランタン東川・事業所番号0173100371）の定員と休止の有無を確認する。同事業所は北海道の指定事業所一覧には掲載されているが、介護サービス情報公表システムに掲載がなく、受託者からは定員を把握できない。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。残るのは入所者数・空床・休止床と、特養・老健・グループホームの定員である（住まいと施設の公表名簿との突合 06シート）。</t>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地）、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -642,7 +642,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>必要事項の一覧（令和8年8月4日現在）</t>
+          <t>必要事項の一覧（令和8年8月5日現在）</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大5件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月4日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大5件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月5日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計した。3調査は点検事項32件（重大5件）の解消を待って計画本文へ反映する。</t>
+          <t>4調査すべてを受領し集計した。3調査は点検事項33件（重大5件）の解消を待って計画本文へ反映する。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項32件の解消待ち】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項33件の解消待ち】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が19件ある（実施済み3調査の受領点検と集計 02シート）。</t>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が20件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項32件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
+          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項33件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -973,12 +973,12 @@
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべてを受領し集計した。3調査は点検事項33件（重大5件）の解消を待って計画本文へ反映する。</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章41表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項33件（重大5件）の取扱いによる。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>素案は第10稿まで作成済み。第6章の見込量・保険料が未算定。</t>
+          <t>素案は第11稿まで作成済み。第2章に調査結果と供給構造を反映した。第6章の見込量・保険料が未算定。</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は第10稿（542段落97表34図）。組版前のため頁数が未確定。</t>
+          <t>素案は第11稿（620段落108表34図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -5209,13 +5209,13 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>点検事項の重大5件の取扱い（No.1〜No.3・No.31）</t>
+          <t>点検事項の重大5件の取扱い（No.1〜No.3・No.31・No.32）</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章41表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項33件（重大5件）の取扱いによる。</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章41表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項34件（重大5件）の取扱いによる。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項33件の解消待ち】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項34件の解消待ち】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項33件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
+          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項34件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章41表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項34件（重大5件）の取扱いによる。</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章48表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項35件（重大6件）の取扱いによる。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大5件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月5日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大6件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月5日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項34件の解消待ち】</t>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項35件の解消待ち】</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -4370,7 +4370,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項34件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
+          <t>介護人材実態調査の介護職員数を事業所単位で確認するため、①厚生労働省「介護サービスの情報公表システム オープンデータ」のサービス種別ごとのCSV（令和6年12月末時点・令和7年6月末時点）、②乖離のある事業所の個別公表画面（採用者数・退職者数を含む）、③北海道オープンデータポータル「介護サービス事業所データ（位置情報付き）【北海道】」（所在町の特定）を取得し、区域内52事業所程度について突合する。点検事項35件のうちNo.1・No.15〜No.19・No.22・No.23・No.26・No.31が事業所への照会を待たずに解消できる見込みである。取得先は3調査の点検15シートに一覧化した。本作業環境からは接続が制限されているため、受託者の別環境で行う。</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>重大5件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否、老健・通所リハの介護職員数の範囲）の方針と、事業所への照会の要否・方法。</t>
+          <t>重大6件（職員数の二重計上、利用者票の回答の偏りの取扱い、所在地区の集計の可否、老健・通所リハの介護職員数の範囲、区域内最大の特定施設の未回答、区域内の施設数と未回答数）の方針と、事業所への照会の要否・方法。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>点検事項の重大5件の取扱い（No.1〜No.3・No.31・No.32）</t>
+          <t>点検事項の重大6件の取扱い（No.1〜No.3・No.31・No.32・No.34）</t>
         </is>
       </c>
       <c r="D26" s="8" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -3889,17 +3889,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>計画骨子案を素案とは別に作成するか</t>
+          <t>計画骨子案の内容の確認</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>仕様書４（6）は骨子案・素案・最終案・概要版を求めている。受託者は骨子案を素案（第10稿）に統合して先行作成した。</t>
+          <t>仕様書４（6）は骨子案・素案・最終案・概要版を求めている。令和8年8月に骨子案を作成した（11節22表）。</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>確認待ち。別に作成する場合は令和8年11月までに作成する。</t>
+          <t>骨子案 第10節の決定・確認を要する事項12件についてご意向を確認したうえで、令和8年11月に3町の意見を反映して確定する。</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -2684,7 +2684,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>H01を見える化W144（性・年齢調整済み要介護2以上認定率）とするか。目標を「全国平均以下への低下」とするか。H05の合成指標と通いの場単独の2系列の扱い。H12・H16は事業所調査を要するため代理指標へ振り替えるか。</t>
+          <t>H01を見える化W144（性・年齢調整済み要介護2以上認定率）とするか。目標を「全国平均以下への低下」とするか。H05の合成指標と通いの場単独の2系列の扱い。H12・H16は、受領した事業所票に受入困難・BCPの設問がないため代理指標へ振り替えるか。H07・H08は在宅介護実態調査が未実施のため同様の判断を要する。</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章48表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項35件（重大6件）の取扱いによる。</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章50表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項35件（重大6件）の取扱いによる。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -978,7 +978,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章50表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項35件（重大6件）の取扱いによる。</t>
+          <t>4調査すべての集計・クロス集計・分析を完了し、実施済み調査 結果報告書（Word・8章51表39図）及びアンケート調査の集計分析報告書（14シート）として取りまとめた。4調査横断のクロス集計は発注者のご意向により行わない。計画本文への反映は点検事項35件（重大6件）の取扱いによる。</t>
         </is>
       </c>
       <c r="E16" s="8" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1187,7 +1187,7 @@
     <row r="25" ht="104" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大6件の取扱い（資料No.2）、③町別住民基本台帳人口（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月5日現在である。資料の受領及び決定により随時更新する。</t>
+          <t>注1）最も急ぐのは、①令和6〜8年度の事業実績（資料No.1）、②3調査の点検事項の重大6件の取扱い（資料No.2）、③町別の第1号被保険者数（資料No.9）、④人口推計の基礎のご意向の確認（方針No.1）、⑤策定委員会の開催日程（日程No.1）の5件である。①②は仕様書の業務そのものが完了せず、③④は将来推計の起点、⑤は会議支援の起点となる。注2）自給率の計画本文への掲載の可否（方針No.13）は、δに「本指標は自治体向けのため取り扱いに注意」と明記されているため、掲載を前提に図表を作る前に確認を要する。注3）国・道の告示待ち5件は、受託者・発注者のいずれも前に進められない。告示前の素案として記述し、告示後に最終照合する扱いを継続する。注4）本表は令和8年8月5日現在である。資料の受領及び決定により随時更新する。</t>
         </is>
       </c>
     </row>
@@ -1340,371 +1340,371 @@
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項35件の解消待ち】</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が20件ある（実施済み3調査の受領点検と集計 02シート）。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.14
+確認No.8・9
+3調査の点検02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.9
+確認No.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.17
+別管理表B30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>発注者・国保連</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>指定事業所台帳（区域外事業所の所在地、及び地域密着型サービスの定員・休止の状況）</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>区域外の事業所が旭川市か他の市町村かを特定する。あわせて、グループホームくるみの郷（東川町・有限会社プランタン東川・事業所番号0173100371）の定員と休止の有無を確認する。同事業所は北海道の指定事業所一覧には掲載されているが、介護サービス情報公表システムに掲載がなく、受託者からは定員を把握できない。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.18
+確認No.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.8
+確認No.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.5
+確認No.6・38</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>3町</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>令和6年・令和7年の町別住民基本台帳人口（年齢4区分別）</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>第9期計画の推計と社人研推計のどちらが実績に近いかの検証。第10期の人口推計の基礎の選択（方針No.1）の判断材料。令和8年7月30日に見える化A系列（人口・2000〜2050年）を受領し広域計の基礎は固まったが、A系列に町別の値は含まれない。</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>仕様書４（5）将来推計の基礎は整理できたが、社人研推計を用いるか3町の推計へ差し替えるかの判断ができない。第2章第1節の町別の記述及び特定地域の判定（市町村単位）も確定しない。</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）【町別住民基本台帳人口は令和8年8月14日に入手済】</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>町別の伸び率の補正係数を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。町別住民基本台帳人口（年齢5歳階級別・平成31年〜令和7年）は、総務省「住民基本台帳に基づく人口、人口動態及び世帯数」により7年分を入手し、町別の伸び率の突合を完了した（人口推計の補正 05・06シート）。残るのは基準人口である第1号被保険者数の町別内訳で、現在は3町計のみを見える化B4cから得ている。</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>町別の補正係数を算定済みだが適用できない。サービス見込量の町別配分が3町計からの按分にとどまる。第2章第1節の町別の記述と特定地域の判定（市町村単位）は住民基本台帳により作成できる。</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>最高</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.3
 確認No.11
 別管理表B5
-人口推計の基礎の検証07</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項35件の解消待ち】</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が20件ある（実施済み3調査の受領点検と集計 02シート）。</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.14
-確認No.8・9
-3調査の点検02</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G8" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.9
-確認No.16</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>発注者・国保連</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.17
-別管理表B30</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>発注者・国保連</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>指定事業所台帳（区域外事業所の所在地、及び地域密着型サービスの定員・休止の状況）</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>区域外の事業所が旭川市か他の市町村かを特定する。あわせて、グループホームくるみの郷（東川町・有限会社プランタン東川・事業所番号0173100371）の定員と休止の有無を確認する。同事業所は北海道の指定事業所一覧には掲載されているが、介護サービス情報公表システムに掲載がなく、受託者からは定員を把握できない。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.18
-確認No.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.8
-確認No.23</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.5
-確認No.6・38</t>
+人口推計の補正05</t>
         </is>
       </c>
     </row>
@@ -2011,11 +2011,11 @@
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.9 令和6年・令和7年の町別住民基本台帳人口（年齢4</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人</t>
         </is>
       </c>
       <c r="D22" s="15" t="n"/>
@@ -2032,11 +2032,11 @@
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
         </is>
       </c>
       <c r="D23" s="15" t="n"/>
@@ -4796,17 +4796,17 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>資料No.9 町別住民基本台帳人口</t>
+          <t>資料No.9 町別の第1号被保険者数</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>令和6年・令和7年の年齢4区分別。</t>
+          <t>年齢階級別（65〜74歳・75〜84歳・85歳以上）・令和8年3月末。町別住民基本台帳人口は令和8年8月14日に入手済み。</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>方針No.1（人口推計の基礎）の判断材料。</t>
+          <t>町別の補正係数の適用。サービス見込量の町別配分。</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -3859,12 +3859,12 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>本文からの抜粋範囲。仕様書に頁数の指定がない。</t>
+          <t>本文からの抜粋範囲。仕様書に頁数の指定がない。令和8年8月14日に構成案を作成した（9シート）。A4判8頁（表紙＋本文6頁＋裏表紙）を推奨し、本編6章を1章1頁で割り付ける案としている。概要版はパブリックコメント（令和9年1月）に用いるため、パブリックコメント用と最終版の2版構成を提案している。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>未着手。</t>
+          <t>構成案07シートの決定を要する事項6件（①頁数と判型、②体裁及び第9期概要版の有無、③保険料の扱い、④町別の数値の掲載範囲、⑤2版構成の可否、⑥意見提出の方法）のご決定を要する。①②④⑤はR8.10、③⑥はR8.11。</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -865,7 +865,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>No.2 レッドチームレビューの残る対応</t>
+          <t>No.2 自己点検記録の残る対応</t>
         </is>
       </c>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>令和6〜8年度の事業実績が未受領のためプロセス評価ができない。レッドチームレビュー29件のうち資料の受領を要する7件が未解消。</t>
+          <t>令和6〜8年度の事業実績が未受領のためプロセス評価ができない。自己点検記録29件のうち資料の受領を要する7件が未解消。</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>素案は第11稿まで作成済み。第2章に調査結果と供給構造を反映した。第6章の見込量・保険料が未算定。</t>
+          <t>素案は令和8年8月時点の版まで作成済み。第2章に調査結果と供給構造を反映した。第6章の見込量・保険料が未算定。</t>
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。レッドチームレビューNo.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。自己点検記録No.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。レッドチームレビューNo.8・No.19・No.24が未解消。</t>
+          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。自己点検記録No.8・No.19・No.24が未解消。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。レッドチームレビューNo.2・No.9・No.20が未解消。</t>
+          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。自己点検記録No.2・No.9・No.20が未解消。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>第3章の評価が受託者の評価のみとなる。レッドチームレビューNo.15が未解消。</t>
+          <t>第3章の評価が受託者の評価のみとなる。自己点検記録No.15が未解消。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2619,7 +2619,7 @@
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>別管理表A25
-レッドチームNo.28</t>
+自己点検No.28</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2756,7 @@
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>別管理表B29
-レッドチームNo.27</t>
+自己点検No.27</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は第11稿（620段落108表34図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（667段落114表34図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>レッドチームレビュー29件の残る対応</t>
+          <t>自己点検記録29件の残る対応</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -4537,7 +4537,7 @@
     <row r="14" ht="104" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>注1）No.6（将来推計）とNo.7（委員会資料原案）は、それぞれ方針の決定No.1のご意向の確認と日程・体制No.1の確定を待っている。この2件が全体の工程で最も大きな待ちである。注2）No.1の見える化からの追加取得は受託者側で試行するが、システムに当広域連合のデータ登録がない系列（δの過年度値、H1・H2、J、L）は取得できない可能性がある。取得できない場合は代替手段を資料6に記載する。注3）No.2〜No.5は資料の受領を待たずに進められる作業である。令和8年8月中に完了させ、計画素案の次稿（第11稿）に反映する。</t>
+          <t>注1）No.6（将来推計）とNo.7（委員会資料原案）は、それぞれ方針の決定No.1のご意向の確認と日程・体制No.1の確定を待っている。この2件が全体の工程で最も大きな待ちである。注2）No.1の見える化からの追加取得は受託者側で試行するが、システムに当広域連合のデータ登録がない系列（δの過年度値、H1・H2、J、L）は取得できない可能性がある。取得できない場合は代替手段を資料6に記載する。注3）No.2〜No.5は資料の受領を待たずに進められる作業である。令和8年8月中に完了させ、計画素案の次の版に反映する。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>令和6〜8年度の事業実績が未受領のためプロセス評価ができない。自己点検記録29件のうち資料の受領を要する7件が未解消。</t>
+          <t>令和6〜8年度の事業実績が未受領のためプロセス評価ができない。自己点検による指摘29件のうち資料の受領を要する7件が未解消。</t>
         </is>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。自己点検記録No.4（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。受託者の自己点検（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。自己点検記録No.8・No.19・No.24が未解消。</t>
+          <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。受託者の自己点検・No.19・No.24が未解消。</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。自己点検記録No.2・No.9・No.20が未解消。</t>
+          <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。受託者の自己点検・No.9・No.20が未解消。</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>第3章の評価が受託者の評価のみとなる。自己点検記録No.15が未解消。</t>
+          <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>自己点検記録29件の残る対応</t>
+          <t>自己点検による指摘29件の残る対応</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（15件）</t>
+          <t>資料の提供をお願いする事項（17件）</t>
         </is>
       </c>
     </row>
@@ -1755,309 +1755,359 @@
     </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）及び月報（令和8年4月〜7月分）</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>第9期の令和6・7年度の通年の確定値と、令和8年度の各月の進捗。見える化は年度途中で締めた値を収録しており通年の実績が確認できない。第3段階（給付費・保険料）の算定と代表KPI H15の把握に用いる。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>第3段階の給付費の算定が実績によらない仮置きのままとなる。H15の基準値が確定しない。</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.21・No.22
+（R8.8.25の打合せで合意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>給付実績データ（サービス別の利用者数・利用日数等。令和5年度〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>サービス見込量の推定の基礎。月当たりの平均利用者数、利用者1人当たりの利用日数・回数。</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>第2段階の見込量が見える化の値のみによる推定にとどまる。サービス別の精緻化ができない。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>R8.8.31</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.23
+（R8.8.25の打合せで合意）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>認定データの確認06シートNo.5</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr"/>
-      <c r="E21" s="3" t="inlineStr"/>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr"/>
+      <c r="E23" s="3" t="inlineStr"/>
+      <c r="F23" s="3" t="inlineStr"/>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n">
+      <c r="B24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="n"/>
-      <c r="E22" s="15" t="n"/>
-      <c r="F22" s="15" t="n"/>
-      <c r="G22" s="15" t="n"/>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="n"/>
-      <c r="E23" s="15" t="n"/>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="15" t="n"/>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
         </is>
       </c>
       <c r="D24" s="15" t="n"/>
@@ -2068,17 +2118,17 @@
       <c r="I24" s="8" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等</t>
         </is>
       </c>
       <c r="D25" s="15" t="n"/>
@@ -2088,8 +2138,50 @@
       <c r="H25" s="15" t="n"/>
       <c r="I25" s="8" t="n"/>
     </row>
-    <row r="27" ht="104" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="8" t="n"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="8" t="n"/>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2097,14 +2189,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="C22:I22"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="C26:I26"/>
     <mergeCell ref="C24:I24"/>
     <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C27:I27"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H19">
+  <conditionalFormatting sqref="H5:H21">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2122,7 +2214,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）</t>
+          <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）【令和8年8月28日に全国集計結果（令和6〜8年度）を受領。代替により解消】</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1810,7 +1810,7 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>給付実績データ（サービス別の利用者数・利用日数等。令和5年度〜令和7年度）</t>
+          <t>給付実績データ（サービス別の利用者数・利用日数等）【令和8年8月28日に大雪地区広域連合及び構成3町の令和6〜8年度分計12ファイルを受領。令和7年度の集計に不一致があり確認中】</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（17件）</t>
+          <t>資料の提供をお願いする事項（18件）</t>
         </is>
       </c>
     </row>
@@ -1847,288 +1847,312 @@
     </row>
     <row r="17" ht="76" customHeight="1">
       <c r="A17" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業計画作成支援ツールの実績値シート（保険料収納必要額の令和7年度分）【令和8年8月28日に町別3ファイルを受領。令和6年度分のみ】</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>第3段階（給付費・保険料）の算定に用いる標準給付費の構成要素（特定入所者介護サービス費、高額介護サービス費、高額医療合算、審査支払手数料）、地域支援事業費、予定保険料収納率。</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>第3段階の算定が令和6年度の実績のみによるものとなる。</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="76" customHeight="1">
-      <c r="A18" s="4" t="n">
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I19" s="5" t="inlineStr">
-        <is>
-          <t>認定データの確認06シートNo.5</t>
-        </is>
-      </c>
-    </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>認定データの確認06シートNo.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr"/>
-      <c r="I23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr"/>
+      <c r="E24" s="3" t="inlineStr"/>
+      <c r="F24" s="3" t="inlineStr"/>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr"/>
+      <c r="I24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n">
+      <c r="B25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n"/>
-      <c r="E24" s="15" t="n"/>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="15" t="n"/>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等</t>
         </is>
       </c>
       <c r="D25" s="15" t="n"/>
@@ -2139,17 +2163,17 @@
       <c r="I25" s="8" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保</t>
         </is>
       </c>
       <c r="D26" s="15" t="n"/>
@@ -2160,17 +2184,17 @@
       <c r="I26" s="8" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
         </is>
       </c>
       <c r="D27" s="15" t="n"/>
@@ -2180,8 +2204,29 @@
       <c r="H27" s="15" t="n"/>
       <c r="I27" s="8" t="n"/>
     </row>
-    <row r="29" ht="104" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="8" t="n"/>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2189,14 +2234,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C24:I24"/>
     <mergeCell ref="C25:I25"/>
     <mergeCell ref="C27:I27"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H21">
+  <conditionalFormatting sqref="H5:H22">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2214,7 +2259,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（18件）</t>
+          <t>資料の提供をお願いする事項（20件）</t>
         </is>
       </c>
     </row>
@@ -1340,44 +1340,89 @@
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>包括的支援事業（6事業）及び任意事業の実績</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>総合相談支援・権利擁護・包括的継続的ケアマネジメント支援・在宅医療介護連携推進・生活支援体制整備・認知症総合支援の相談件数・実人数・会議回数・事業費。介護給付等費用適正化事業・家族介護支援事業の実績。</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査の対象外であり、公表資料では代替できない。素案 第3章第2節が空欄のままとなる。</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.13（03シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項35件の解消待ち】</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が20件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.14
 確認No.8・9
@@ -1385,321 +1430,321 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="76" customHeight="1">
-      <c r="A7" s="4" t="n">
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.9
 確認No.16</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.17
 別管理表B30</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>指定事業所台帳（区域外事業所の所在地、及び地域密着型サービスの定員・休止の状況）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>区域外の事業所が旭川市か他の市町村かを特定する。あわせて、グループホームくるみの郷（東川町・有限会社プランタン東川・事業所番号0173100371）の定員と休止の有無を確認する。同事業所は北海道の指定事業所一覧には掲載されているが、介護サービス情報公表システムに掲載がなく、受託者からは定員を把握できない。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.18
 確認No.30</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。受託者の自己点検（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.7</t>
-        </is>
-      </c>
-    </row>
     <row r="11" ht="76" customHeight="1">
       <c r="A11" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。受託者の自己点検（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。受託者の自己点検・No.19・No.24が未解消。</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.8
 確認No.23</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="76" customHeight="1">
-      <c r="A12" s="4" t="n">
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）【令和8年8月28日に全国集計結果（令和6〜8年度）を受領。代替により解消】</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。受託者の自己点検・No.9・No.20が未解消。</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.5
 確認No.6・38</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>3町</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）【町別住民基本台帳人口は令和8年8月14日に入手済】</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>町別の伸び率の補正係数を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。町別住民基本台帳人口（年齢5歳階級別・平成31年〜令和7年）は、総務省「住民基本台帳に基づく人口、人口動態及び世帯数」により7年分を入手し、町別の伸び率の突合を完了した（人口推計の補正 05・06シート）。残るのは基準人口である第1号被保険者数の町別内訳で、現在は3町計のみを見える化B4cから得ている。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>町別の補正係数を算定済みだが適用できない。サービス見込量の町別配分が3町計からの按分にとどまる。第2章第1節の町別の記述と特定地域の判定（市町村単位）は住民基本台帳により作成できる。</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.3
 確認No.11
@@ -1708,493 +1753,496 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>受給者数データの確認06シートNo.1・No.9</t>
-        </is>
-      </c>
-    </row>
     <row r="15" ht="76" customHeight="1">
       <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>受給者数データの確認06シートNo.1・No.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>介護保険事業状況報告　年報（令和6年度・令和7年度）及び月報（令和8年4月〜7月分）</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>第9期の令和6・7年度の通年の確定値と、令和8年度の各月の進捗。見える化は年度途中で締めた値を収録しており通年の実績が確認できない。第3段階（給付費・保険料）の算定と代表KPI H15の把握に用いる。</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>第3段階の給付費の算定が実績によらない仮置きのままとなる。H15の基準値が確定しない。</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.21・No.22
 （R8.8.25の打合せで合意）</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="76" customHeight="1">
-      <c r="A16" s="4" t="n">
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>給付実績データ（サービス別の利用者数・利用日数等）【令和8年8月28日に大雪地区広域連合及び構成3町の令和6〜8年度分計12ファイルを受領。令和7年度の集計に不一致があり確認中】</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>サービス見込量の推定の基礎。月当たりの平均利用者数、利用者1人当たりの利用日数・回数。</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>第2段階の見込量が見える化の値のみによる推定にとどまる。サービス別の精緻化ができない。</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>R8.8.31</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G17" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.23
 （R8.8.25の打合せで合意）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="76" customHeight="1">
-      <c r="A17" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>介護保険事業計画作成支援ツールの実績値シート（保険料収納必要額の令和7年度分）【令和8年8月28日に町別3ファイルを受領。令和6年度分のみ】</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>第3段階（給付費・保険料）の算定に用いる標準給付費の構成要素（特定入所者介護サービス費、高額介護サービス費、高額医療合算、審査支払手数料）、地域支援事業費、予定保険料収納率。</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>第3段階の算定が令和6年度の実績のみによるものとなる。</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>確認事項No.47</t>
-        </is>
-      </c>
-    </row>
     <row r="18" ht="76" customHeight="1">
       <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>介護保険事業計画作成支援ツールの実績値シート（保険料収納必要額の令和7年度分）【令和8年8月28日に町別3ファイルを受領。令和6年度分のみ】</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>第3段階（給付費・保険料）の算定に用いる標準給付費の構成要素（特定入所者介護サービス費、高額介護サービス費、高額医療合算、審査支払手数料）、地域支援事業費、予定保険料収納率。</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>第3段階の算定が令和6年度の実績のみによるものとなる。</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査の令和7年度分【令和8年8月28日に令和6年度分（市町村Ⅰ・Ⅱ・Ⅲ）を受領】</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>第9期の通いの場と地域支援事業の実績。代表KPI H05（総合事業ベース）の令和7年度の値。</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>第9期の評価が令和6年度の断面のみとなり、施策の効果が一時的なものかどうかを判断できない。</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="76" customHeight="1">
-      <c r="A19" s="4" t="n">
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G19" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="76" customHeight="1">
-      <c r="A20" s="4" t="n">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>認定データの確認06シートNo.5</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="G21" s="13" t="inlineStr">
+      <c r="G23" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="4" t="n">
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr"/>
-      <c r="F24" s="3" t="inlineStr"/>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr"/>
+      <c r="E26" s="3" t="inlineStr"/>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr"/>
+      <c r="I26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n"/>
-      <c r="E25" s="15" t="n"/>
-      <c r="F25" s="15" t="n"/>
-      <c r="G25" s="15" t="n"/>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-      <c r="G26" s="15" t="n"/>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="8" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
       <c r="B27" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.19 包括的支援事業（6事業）及び任意事業の実績</t>
         </is>
       </c>
       <c r="D27" s="15" t="n"/>
@@ -2205,17 +2253,17 @@
       <c r="I27" s="8" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
         </is>
       </c>
       <c r="D28" s="15" t="n"/>
@@ -2225,8 +2273,50 @@
       <c r="H28" s="15" t="n"/>
       <c r="I28" s="8" t="n"/>
     </row>
-    <row r="30" ht="104" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="8" t="n"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="8" t="n"/>
+    </row>
+    <row r="32" ht="104" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2236,12 +2326,12 @@
   <mergeCells count="6">
     <mergeCell ref="C28:I28"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C30:I30"/>
     <mergeCell ref="C27:I27"/>
-    <mergeCell ref="A30:I30"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H22">
+  <conditionalFormatting sqref="H5:H24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2259,7 +2349,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1840,7 +1840,7 @@
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.21・No.22
-（R8.8.25の打合せで合意）</t>
+（R8.8.26の打合せで合意）</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.23
-（R8.8.25の打合せで合意）</t>
+（R8.8.26の打合せで合意）</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（20件）</t>
+          <t>資料の提供をお願いする事項（21件）</t>
         </is>
       </c>
     </row>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="6" ht="76" customHeight="1">
       <c r="A6" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
@@ -1349,22 +1349,22 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>包括的支援事業（6事業）及び任意事業の実績</t>
+          <t>介護保険事業状況報告　年報（令和7年度）の様式4・様式4の2・様式4の3及び経理状況【令和8年8月28日に年報2か年と月報4か月分を受領。令和7年度の様式4以降は全項目0で未入力】</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>総合相談支援・権利擁護・包括的継続的ケアマネジメント支援・在宅医療介護連携推進・生活支援体制整備・認知症総合支援の相談件数・実人数・会議回数・事業費。介護給付等費用適正化事業・家族介護支援事業の実績。</t>
+          <t>令和7年度末の介護給付費準備基金の残高と決算額。令和6年度末の基金保有額231,689,018円は受領により確定したが、第10期の保険料算定には直近（令和7年度末）の残高が必要である。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>総合事業の実施状況に関する調査の対象外であり、公表資料では代替できない。素案 第3章第2節が空欄のままとなる。</t>
+          <t>第10期の保険料算定における取崩額を設定できない。素案 第6章第6節が［要確認］のままとなる。</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1379,50 +1379,96 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.13（03シート）</t>
+          <t>資料依頼No.21
+年報月報の受領点検 04シート</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1">
       <c r="A7" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>包括的支援事業（6事業）及び任意事業の実績</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>総合相談支援・権利擁護・包括的継続的ケアマネジメント支援・在宅医療介護連携推進・生活支援体制整備・認知症総合支援の相談件数・実人数・会議回数・事業費。介護給付等費用適正化事業・家族介護支援事業の実績。</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>総合事業の実施状況に関する調査の対象外であり、公表資料では代替できない。素案 第3章第2節が空欄のままとなる。</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>最高</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.13（03シート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>在宅生活改善調査・居所変更実態調査・介護人材実態調査の第10期分（調査票、回答データ、集計資料、分析資料、報告書）【令和8年8月4日に102ファイルを受領。点検事項35件の解消待ち】</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>4調査横断のクロス集計。代表KPI H06・H11・H13・H14の基準値の設定。</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>受領済。点検の結果、集計方法を決めないと計画本文の数値が変わる事項が5件（職員数の二重計上、利用者票の回答の偏り、所在地区の記入形式、老健・通所リハの介護職員数と見える化の乖離、区域内最大の特定施設が居所変更実態調査に回答していないこと）ある。事業所への照会により解消できる事項が20件ある（実施済み3調査の受領点検と集計 02シート）。</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>R8.8</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>実施中</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.14
 確認No.8・9
@@ -1430,321 +1476,321 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="76" customHeight="1">
-      <c r="A8" s="4" t="n">
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>決算書及び介護給付費準備基金の積立・取崩実績（第7期〜第9期各年度、令和8年度末残高見込を含む）</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>第9期の剰余が基金に積み立てられた額との一致の確認。第10期の基金取崩額の決定。</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>第6章第6節の保険料試算が確定しない。剰余の月額（＋385円）は見える化C1で確定したが金額の確認が必要。</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.9
 確認No.16</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="76" customHeight="1">
-      <c r="A9" s="4" t="n">
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>町別・サービス区分別の給付費（令和4〜7年度）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>自給率と掛け合わせて区域外への給付費の流出額を算定する。自給率の6区分平均を加重平均にする。</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>給付費の地域内還流の議論（第6章第5節）が割合の記述にとどまる。</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.17
 別管理表B30</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="76" customHeight="1">
-      <c r="A10" s="4" t="n">
+    <row r="11" ht="76" customHeight="1">
+      <c r="A11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>発注者・国保連</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>指定事業所台帳（区域外事業所の所在地、及び地域密着型サービスの定員・休止の状況）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>区域外の事業所が旭川市か他の市町村かを特定する。あわせて、グループホームくるみの郷（東川町・有限会社プランタン東川・事業所番号0173100371）の定員と休止の有無を確認する。同事業所は北海道の指定事業所一覧には掲載されているが、介護サービス情報公表システムに掲載がなく、受託者からは定員を把握できない。認知症対応型共同生活介護は地域密着型サービスであり、指定権者は大雪地区広域連合である。</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>圏域を越えた利用の調整（第6章第4節）の根拠が示せない。24時間対応サービスの確保方策の判断材料が欠ける。</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.18
 確認No.30</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="76" customHeight="1">
-      <c r="A11" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量と第5節の整備方針が確定しない。受託者の自己点検（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>資料依頼No.7</t>
-        </is>
-      </c>
-    </row>
     <row r="12" ht="76" customHeight="1">
       <c r="A12" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>発注者・3町</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>事業所・施設の定員と稼働の実績（①地域密着型通所介護4事業所の定員・登録者数・延べ利用者数、②施設・居住系の定員・入所者数・空床・休止床、③介護老人福祉施設の定員減少234人→160人の経緯）</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>稼働率の低下の有無の確認。定員減少の経緯の特定。第10期基本指針案の別表 七が求める入所率・稼働率の把握。</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節の見込量と第5節の整備方針が確定しない。受託者の自己点検（地域密着型通所介護）が未解消。令和8年8月4日に北海道の施設・住まいの名簿5種を受領し、特定施設156人・住宅型有料223人・サービス付き高齢者向け住宅66戸・軽費老人ホーム50人の定員が確定した。特別養護老人ホーム名簿により特養160人・地域密着型特養62人も確定し、公表システムの個別画面によりグループホームファミリー18人を確認した。残るのは入所者数・空床・休止床と、グループホームくるみの郷1事業所の定員である（住まいと施設の公表名簿との突合 06・09・10シート）。</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>資料依頼No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>未利用認定者の内訳とケアプランのサービス構成（①居宅サービス計画未作成者の要介護度別内訳、②認定から初回利用までの期間、③新規認定者数と認定申請件数の推移、④訪問介護と通所介護の同一利用者の組合せ）</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>利用率低下の要因の分解。訪問と通所の代替関係の検証。要介護5の受給率低下の要因の特定。</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>第2章第2節の中心論点（利用率低下）が要因未特定のままとなる。受託者の自己点検・No.19・No.24が未解消。</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>R8.10</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.8
 確認No.23</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="76" customHeight="1">
-      <c r="A13" s="4" t="n">
+    <row r="14" ht="76" customHeight="1">
+      <c r="A14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>保険者機能強化推進交付金等の評価調書（令和4〜7年度分）【令和8年8月28日に全国集計結果（令和6〜8年度）を受領。代替により解消】</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>①0点10項目が取組の不在か要件未充足かの判別、②成果指標の分子・分母の実数、③評価対象期間の確認、④令和6年・令和7年調査の得点。</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>第3章第4節の交付金評価の解釈が確定しない。W144（H01の測定指標）の上昇の要因が説明できない。受託者の自己点検・No.9・No.20が未解消。</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.5
 確認No.6・38</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="76" customHeight="1">
-      <c r="A14" s="4" t="n">
+    <row r="15" ht="76" customHeight="1">
+      <c r="A15" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>3町</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>町別の第1号被保険者数（年齢階級別・令和8年3月末）【町別住民基本台帳人口は令和8年8月14日に入手済】</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>町別の伸び率の補正係数を適用するための基準人口。65〜74歳・75〜84歳・85歳以上の3階級。町別住民基本台帳人口（年齢5歳階級別・平成31年〜令和7年）は、総務省「住民基本台帳に基づく人口、人口動態及び世帯数」により7年分を入手し、町別の伸び率の突合を完了した（人口推計の補正 05・06シート）。残るのは基準人口である第1号被保険者数の町別内訳で、現在は3町計のみを見える化B4cから得ている。</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>町別の補正係数を算定済みだが適用できない。サービス見込量の町別配分が3町計からの按分にとどまる。第2章第1節の町別の記述と特定地域の判定（市町村単位）は住民基本台帳により作成できる。</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.3
 確認No.11
@@ -1753,54 +1799,9 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="76" customHeight="1">
-      <c r="A15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>受給者数データの確認06シートNo.1・No.9</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="76" customHeight="1">
       <c r="A16" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
@@ -1809,22 +1810,22 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告　年報（令和6年度・令和7年度）及び月報（令和8年4月〜7月分）</t>
+          <t>居住系・施設サービスの種別別受給者数と総合事業の実績【要介護度別の認定者数・利用率・1人当たり利用日数は受領済】</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>第9期の令和6・7年度の通年の確定値と、令和8年度の各月の進捗。見える化は年度途中で締めた値を収録しており通年の実績が確認できない。第3段階（給付費・保険料）の算定と代表KPI H15の把握に用いる。</t>
+          <t>第2段階（サービス見込量）の算定チェーンは、令和8年8月4日に受領した見える化B3系列・D45系列・D46系列により閉じた（サービス受給者数データの確認 05シートで検証済み）。残るのは、①グループホーム・特定施設・地域密着型特養など居住系及び施設サービスの種別別の受給者数、②介護予防・日常生活支援総合事業の実績である。</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>第3段階の給付費の算定が実績によらない仮置きのままとなる。H15の基準値が確定しない。</t>
+          <t>サービス種別ごとの見込量の様式が確定しない。①は施設・居住系を定員により見込むため代替できるが、②の総合事業は広域連合の実績によるほかない。</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
@@ -1839,8 +1840,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.21・No.22
-（R8.8.26の打合せで合意）</t>
+          <t>受給者数データの確認06シートNo.1・No.9</t>
         </is>
       </c>
     </row>
@@ -1982,288 +1982,312 @@
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>月報のExcel形式の原本（令和8年4月分以降）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>月報はスキャンしたPDFであり、文字認識に誤りがある（「1,102」を「1021」と読むなど）。年報と同じExcel形式であれば誤りなく取り込める。困難な場合は、受託者が読み取った値のご確認でも足りる。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の各月の値を計画本文に用いる前に、原本との目視の照合が必要となる。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>認定データの確認06シートNo.5</t>
-        </is>
-      </c>
-    </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>認定データの確認06シートNo.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="76" customHeight="1">
-      <c r="A24" s="4" t="n">
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr"/>
-      <c r="F26" s="3" t="inlineStr"/>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr"/>
-      <c r="I26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr"/>
+      <c r="E27" s="3" t="inlineStr"/>
+      <c r="F27" s="3" t="inlineStr"/>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.19 包括的支援事業（6事業）及び任意事業の実績</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="15" t="n"/>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="8" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
       <c r="B28" s="5" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.15 介護保険事業状況報告　年報（令和6年度・令和7年、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.15 介護保険事業状況報告　年報（令和7年度）の様式4、No.19 包括的支援事業（6事業）及び任意事業の実績</t>
         </is>
       </c>
       <c r="D28" s="15" t="n"/>
@@ -2274,17 +2298,17 @@
       <c r="I28" s="8" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.20 月報のExcel形式の原本（令和8年4月分以降）、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
         </is>
       </c>
       <c r="D29" s="15" t="n"/>
@@ -2295,17 +2319,17 @@
       <c r="I29" s="8" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
         </is>
       </c>
       <c r="D30" s="15" t="n"/>
@@ -2315,8 +2339,29 @@
       <c r="H30" s="15" t="n"/>
       <c r="I30" s="8" t="n"/>
     </row>
-    <row r="32" ht="104" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="8" t="n"/>
+    </row>
+    <row r="33" ht="104" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2325,13 +2370,13 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C31:I31"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A33:I33"/>
     <mergeCell ref="C29:I29"/>
     <mergeCell ref="C30:I30"/>
-    <mergeCell ref="C27:I27"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H24">
+  <conditionalFormatting sqref="H5:H25">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2349,7 +2394,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -1982,26 +1982,26 @@
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>美瑛町・3町</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>月報のExcel形式の原本（令和8年4月分以降）</t>
+          <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>月報はスキャンしたPDFであり、文字認識に誤りがある（「1,102」を「1021」と読むなど）。年報と同じExcel形式であれば誤りなく取り込める。困難な場合は、受託者が読み取った値のご確認でも足りる。</t>
+          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>令和8年度の各月の値を計画本文に用いる前に、原本との目視の照合が必要となる。</t>
+          <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2009,9 +2009,9 @@
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2021,32 +2021,33 @@
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>資料依頼No.12
+確認No.20</t>
         </is>
       </c>
     </row>
     <row r="21" ht="76" customHeight="1">
       <c r="A21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>美瑛町・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小学校区と日常生活圏域の対応関係</t>
+          <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
+          <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
+          <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2066,14 +2067,14 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.12
-確認No.20</t>
+          <t>資料依頼No.15
+確認No.7</t>
         </is>
       </c>
     </row>
     <row r="22" ht="76" customHeight="1">
       <c r="A22" s="4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
@@ -2082,22 +2083,22 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>受託者の評価との対照。評価の枠組みの整理。</t>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>R8.9</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -2112,14 +2113,13 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>資料依頼No.15
-確認No.7</t>
+          <t>認定データの確認06シートNo.5</t>
         </is>
       </c>
     </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -2128,22 +2128,22 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
+          <t>令和8年8月分以降の月報（PDFで差し支えない）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
+          <t>令和8年度の各月の推移。令和8年4〜7月分は画像の目視により値を確定済みであり、PDFのままで支障ない。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
+          <t>令和8年度の実績の推定が7月までの4か月にとどまる。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>毎月</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>認定データの確認06シートNo.5</t>
+          <t>年報月報の受領点検 04シート</t>
         </is>
       </c>
     </row>
@@ -2304,11 +2304,11 @@
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.20 月報のExcel形式の原本（令和8年4月分以降）、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
         </is>
       </c>
       <c r="D29" s="15" t="n"/>
@@ -2325,11 +2325,11 @@
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜、No.20 令和8年8月分以降の月報（PDFで差し支えない）</t>
         </is>
       </c>
       <c r="D30" s="15" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1234,7 +1234,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>資料の提供をお願いする事項（21件）</t>
+          <t>資料の提供をお願いする事項（23件）</t>
         </is>
       </c>
     </row>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告　年報（令和7年度）の様式4・様式4の2・様式4の3及び経理状況【令和8年8月28日に年報2か年と月報4か月分を受領。令和7年度の様式4以降は全項目0で未入力】</t>
+          <t>令和7年度の決算書（介護保険特別会計）又は年報（令和7年度）の様式4・経理状況【令和8年8月28日に年報2か年・月報4か月分・令和6年度決算書を受領。令和7年度の様式4以降は未入力】</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>令和7年度末の介護給付費準備基金の残高と決算額。令和6年度末の基金保有額231,689,018円は受領により確定したが、第10期の保険料算定には直近（令和7年度末）の残高が必要である。</t>
+          <t>令和7年度末の介護給付費準備基金の残高と決算額。令和6年度は決算書と年報の双方により確定した（年度末残高231,689,018円、前年度末231,456,821円、取崩し0円）。第10期の保険料算定には直近（令和7年度末）の残高が必要である。決算の調製は例年12月に議会へ提出されている。</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>R8.10</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -1380,7 +1380,7 @@
       <c r="I6" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.21
-年報月報の受領点検 04シート</t>
+令和6年度決算書の受領点検 04シート</t>
         </is>
       </c>
     </row>
@@ -1982,144 +1982,144 @@
     </row>
     <row r="20" ht="76" customHeight="1">
       <c r="A20" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の予算書（介護保険特別会計）</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>第9期最終年度の見込み。令和8年度の決算は本業務の期間中に確定しないため、予算額により見込みを立てる。</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>第9期末の基金残高の見込みが立たない。</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度決算書の受領点検 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>美瑛町・3町</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>小学校区と日常生活圏域の対応関係</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>健康とくらしの調査の分析地域1（小学校区12地区）と第9期の6圏域の対応。美馬牛小学校区以外が不明である。</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>圏域別の分析ができない。第1章第7節の圏域設定の見直しが確定しない。</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.12
 確認No.20</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="76" customHeight="1">
-      <c r="A21" s="4" t="n">
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>第9期の自己評価と北海道への報告の実績（介護保険法第117条に基づく評価・公表）</t>
         </is>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>受託者の評価との対照。評価の枠組みの整理。</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>第3章の評価が受託者の評価のみとなる。受託者の自己点検が未解消。</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>R8.9</t>
         </is>
       </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.15
 確認No.7</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="76" customHeight="1">
-      <c r="A22" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>認定データの確認06シートNo.5</t>
-        </is>
-      </c>
-    </row>
     <row r="23" ht="76" customHeight="1">
       <c r="A23" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -2128,22 +2128,22 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>令和8年8月分以降の月報（PDFで差し支えない）</t>
+          <t>区分変更の申請件数と変更前後の要介護度（令和元〜令和7年度）</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>令和8年度の各月の推移。令和8年4〜7月分は画像の目視により値を確定済みであり、PDFのままで支障ない。</t>
+          <t>新規認定者に占める要支援1の割合が令和4年度18.1％から令和6年度27.9％へ上昇している一方、認定者全体では要介護1が7年間で91人増えている。要支援から要介護1への移行が起きているかを確認するために必要である。</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>令和8年度の実績の推定が7月までの4か月にとどまる。</t>
+          <t>第2章第2節の要介護度別の推移の要因が特定できない。第5章基本目標1（介護予防）の効果の測定ができない。</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>毎月</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -2158,178 +2158,226 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>年報月報の受領点検 04シート</t>
+          <t>認定データの確認06シートNo.5</t>
         </is>
       </c>
     </row>
     <row r="24" ht="76" customHeight="1">
       <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>令和8年8月分以降の月報（PDFで差し支えない）</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の各月の推移。令和8年4〜7月分は画像の目視により値を確定済みであり、PDFのままで支障ない。</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度の実績の推定が7月までの4か月にとどまる。</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>毎月</t>
+        </is>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>年報月報の受領点検 04シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="76" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>介護給付費準備基金条例</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>基金の正式名称と、積立て・処分の要件。決算書は「介護保険事業財政調整基金」、年報は「介護給付費準備基金」としている。</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>計画本文に用いる名称が確定しない。取崩しの要件を計画に記載できない。</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>確認待ち</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="76" customHeight="1">
+      <c r="A26" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>北海道・広域連合</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>訪問系・通所系事業所の運営規程における「通常の事業の実施地域」【令和8年8月4日受領済】</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>訪問・通所困難地域の判定の唯一の客観的根拠。居宅サービスは北海道、地域密着型は広域連合が保有する。</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>解消。北海道の介護保険事業所一覧（令和8年6月30日現在・47区分）に「通常の事業実施地域」が収録されており、区域内の指定事業所124件を抽出して整理した（住まいと施設の公表名簿との突合 08シート）。訪問介護13事業所のうち美瑛町を実施地域とするのは4事業所、東川町は5事業所、東神楽町は6事業所である。残るのは実施地域欄が空欄の3事業所の取扱いのみ。</t>
         </is>
       </c>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>受領済</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G26" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.2
 確認No.15</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="76" customHeight="1">
-      <c r="A25" s="4" t="n">
+    <row r="27" ht="76" customHeight="1">
+      <c r="A27" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>総務省・3町</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>令和7年国勢調査による町別の高齢者を含む世帯</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>高齢者単身世帯・夫婦世帯の最新値。</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>第2章第1節の世帯構成が令和2年国勢調査のままとなる。</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>公表後</t>
         </is>
       </c>
-      <c r="G25" s="13" t="inlineStr">
+      <c r="G27" s="13" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>確認待ち</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>資料依頼No.4</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="14" t="inlineStr">
         <is>
           <t>最高</t>
         </is>
       </c>
-      <c r="B28" s="5" t="n">
+      <c r="B30" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.15 介護保険事業状況報告　年報（令和7年度）の様式4、No.19 包括的支援事業（6事業）及び任意事業の実績</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n"/>
-      <c r="E28" s="15" t="n"/>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="15" t="n"/>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="32" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n"/>
-      <c r="E29" s="15" t="n"/>
-      <c r="F29" s="15" t="n"/>
-      <c r="G29" s="15" t="n"/>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="32" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>4</v>
-      </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜、No.20 令和8年8月分以降の月報（PDFで差し支えない）</t>
+          <t>No.1 令和6〜8年度の施策・事業実績、事業量、対象実人、No.15 令和7年度の決算書（介護保険特別会計）又は年報（、No.19 包括的支援事業（6事業）及び任意事業の実績</t>
         </is>
       </c>
       <c r="D30" s="15" t="n"/>
@@ -2340,17 +2388,17 @@
       <c r="I30" s="8" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>低</t>
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>高</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+          <t>No.2 在宅生活改善調査・居所変更実態調査・介護人材実態、No.3 決算書及び介護給付費準備基金の積立・取崩実績（第、No.4 町別・サービス区分別の給付費（令和4〜7年度）、No.5 指定事業所台帳（区域外事業所の所在地、及び地域密、No.6 事業所・施設の定員と稼働の実績（①地域密着型通所、No.7 未利用認定者の内訳とケアプランのサービス構成（①、No.8 保険者機能強化推進交付金等の評価調書（令和4〜7、No.9 町別の第1号被保険者数（年齢階級別・令和8年3月、No.14 居住系・施設サービスの種別別受給者数と総合事業の、No.21 令和8年度の予算書（介護保険特別会計）、No.16 給付実績データ（サービス別の利用者数・利用日数等、No.17 介護保険事業計画作成支援ツールの実績値シート（保、No.18 総合事業の実施状況に関する調査の令和7年度分【令</t>
         </is>
       </c>
       <c r="D31" s="15" t="n"/>
@@ -2360,8 +2408,50 @@
       <c r="H31" s="15" t="n"/>
       <c r="I31" s="8" t="n"/>
     </row>
-    <row r="33" ht="104" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜、No.22 介護給付費準備基金条例、No.20 令和8年8月分以降の月報（PDFで差し支えない）</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="8" t="n"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>No.10 訪問系・通所系事業所の運営規程における「通常の事、No.13 令和7年国勢調査による町別の高齢者を含む世帯</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="8" t="n"/>
+    </row>
+    <row r="35" ht="104" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>注1）最高優先の3件は、いずれも仕様書の業務そのものが完了しない資料である。No.1（事業実績）は仕様書４（2）、No.2（3調査）は同（3）、No.9（町別住基人口）は同（5）に対応する。注2）令和8年7月30日に見える化δ（自給率）・D49（地域差指数）・C1（保険料と必要額）を受領し、従前の依頼のうち2件が解消（第7期の保険料条例、自給率の算定）、1件が一部解消（給付実績情報）した。注3）本表は「資料の提供」を求めるものであり、「決定」を求めるものは02シートに分けている。資料の受領後に算定方法の確認を要するものがあるため、1つの論点が両方に現れることがある。</t>
         </is>
@@ -2369,14 +2459,14 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="C28:I28"/>
     <mergeCell ref="C31:I31"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C32:I32"/>
     <mergeCell ref="C30:I30"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="A35:I35"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H25">
+  <conditionalFormatting sqref="H5:H27">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"完了"</formula>
     </cfRule>
@@ -2394,7 +2484,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"完了,実施中,確認待ち,未着手,対象外"</formula1>
     </dataValidation>
   </dataValidations>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -2218,17 +2218,17 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>介護給付費準備基金条例</t>
+          <t>第9期計画の保険料算定の資料（保険料収納必要額の算定過程）【基金条例は令和8年8月28日に受領。基金の名称・処分の要件・積立ての上限を確認済み】</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>基金の正式名称と、積立て・処分の要件。決算書は「介護保険事業財政調整基金」、年報は「介護給付費準備基金」としている。</t>
+          <t>条例第5条第3項の上限は「介護保険事業計画で算定する介護保険料必要収納額の100分の10」である。受託者は第9期計画による3か年計2,051,968,467円を用いているが、算定過程の資料により確認したい。</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>計画本文に用いる名称が確定しない。取崩しの要件を計画に記載できない。</t>
+          <t>積立ての上限の算定が受託者の読み取りによるものにとどまる。第10期の取崩方針の根拠が弱くなる。</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.52</t>
+          <t>確認事項No.53</t>
         </is>
       </c>
     </row>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜、No.22 介護給付費準備基金条例、No.20 令和8年8月分以降の月報（PDFで差し支えない）</t>
+          <t>No.11 小学校区と日常生活圏域の対応関係、No.12 第9期の自己評価と北海道への報告の実績（介護保険、No.19 区分変更の申請件数と変更前後の要介護度（令和元〜、No.22 第9期計画の保険料算定の資料（保険料収納必要額の、No.20 令和8年8月分以降の月報（PDFで差し支えない）</t>
         </is>
       </c>
       <c r="D32" s="15" t="n"/>

--- a/output/第10期計画_必要事項の一覧.xlsx
+++ b/output/第10期計画_必要事項の一覧.xlsx
@@ -4121,7 +4121,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>素案は令和8年8月時点の版（667段落114表34図）。組版前のため頁数が未確定。</t>
+          <t>素案は令和8年8月時点の版（806段落130表36図）。組版前のため頁数が未確定。</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
